--- a/doc/QTL - Task Tracker (June 2026).xlsx
+++ b/doc/QTL - Task Tracker (June 2026).xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$222</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6928,8 +6928,368 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Location access: all shops, one shop, or a chosen few</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>A user could only have their own shop or every shop. The Users screen now offers All, Single or Multiple, and Multiple lets you tick exactly which shops that person can see and work in.</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F211" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Dates no longer jump to tomorrow after 8 PM</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>The server runs on UTC time, so from 8 PM Ontario time new payments, customers, exports and date defaults were stamped with the next day's date. Every 'today' in the app now uses the Ontario calendar day and switches between EDT and EST by itself, and dates and times display the same way on every page.</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Fixed part prices now follow cost</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>103 parts had an Over the Counter price typed in from the May 2026 sheet, so changing their cost or margin did not change what a customer paid. Each fixed price was turned into the matching margin. Every price is the same today, and from now on it moves when the cost changes.</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Parts list flags prices that won't follow cost</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>A part that still has a tier held at a fixed price now says 'some prices fixed' or 'sell price fixed' under its List price, so it's clear why editing the cost doesn't change it.</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Pricing &amp; Catalogue</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Bundled parts show their With Service price again</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>FF252, FF4212800MX-NN, FF5206 and the other 77 bundled parts showed $0.00 for With Service on the All filter sell price list and in the part editor. They now show the calculated price (FF252 $55.99, FF4212800MX-NN $29.99, FF5206 $7.99) with a small 'bundled' tag. On a job a bundled part still charges $0 at With Service, because the package already covers it. FF4212800MX-NN also had a -$29.71 service charge cancelling out its cost, which was cleared.</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Oil detail limited to Owner and Admin</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>Oil detail is now hidden from Manager, Accountant, Staff, Supervisor and Technician, both in the menu and when the page link is opened directly.</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Each Pricing page has its own permission</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>Pricing used to be one permission covering all of its pages. Oil detail, Oil grid, Print list, Trans &amp; Diff and the other Pricing pages can now each be turned on or off for a user.</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F217" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Export CSV removed for Staff</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>Staff no longer see Export CSV on Customers or Inventory. The export links refuse Staff too, so the file can't be downloaded from a direct link either.</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Actions section on the permissions screen</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Settings &gt; Users has a new Actions section for buttons such as Export CSV, so an action can be given to or taken away from one user without a code change.</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F219" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard removed for Manager, Vendors removed for Staff</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Jaimie (Manager) and Yadwinder (Staff) could still open Dashboard and Vendors because of old per-user settings. Those settings now match the role defaults. Nobody was left without any pages.</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>Multi-location managers can edit invoices at any shop</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Jaimie could not save changes to Fort Erie or Napanee invoices. The invoice header saved, but its line items were blocked outside her home shop, so the save failed. Line items now have the same shop access as the invoice they belong to.</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F221" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>A blank price box can never mean $0</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>A blank fixed-price box could have been saved as a $0 price, which would override the formula and sell the part for nothing. A blank box is now always saved as 'no fixed price'. The parts screen never sent a blank, so no part was affected.</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F222" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F210"/>
+  <autoFilter ref="A1:F222"/>
   <conditionalFormatting sqref="A2:E191">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F2="Feature"</formula>
@@ -6982,11 +7342,10 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>209 tasks · 2026-05-30 to 2026-09-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>221 tasks · 2026-05-30 to 2026-09-11</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -7001,7 +7360,7 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -7011,7 +7370,7 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -7021,10 +7380,9 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8"/>
+        <v>50</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
@@ -7142,16 +7500,16 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -7172,7 +7530,7 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -7182,7 +7540,7 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -7198,17 +7556,17 @@
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Roles &amp; Permissions</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>Vendors &amp; Expenses</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
@@ -7218,17 +7576,17 @@
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Oil Grid &amp; Pricing</t>
+          <t>Vendors &amp; Expenses</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions</t>
+          <t>Oil Grid &amp; Pricing</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
@@ -7268,17 +7626,17 @@
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Pricing &amp; Catalogue</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>Pricing &amp; Catalogue</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="B29" s="22" t="n">

--- a/doc/QTL - Task Tracker (June 2026).xlsx
+++ b/doc/QTL - Task Tracker (June 2026).xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$246</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7288,9 +7288,729 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Users page no longer crashes</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Settings &gt; Users showed an application error because the new Actions permissions needed a database update that hadn't been applied yet. The page now loads whether or not that update is in.</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Vendors &amp; Expenses</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Recurring expenses run automatically again</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>The daily job that creates recurring expenses runs with nobody signed in, so it was being sent to the login page and never ran. It now gets through, and still checks its own secret key before doing anything.</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Vendors &amp; Expenses</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Expense lines saved at any shop</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>A manager or staff member with access to more than one shop could save an expense at another shop, but not its lines, so an oil purchase or part on it was refused. Expense lines now have the same shop access as the expense itself.</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Vendors &amp; Expenses</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>Jug quantities like 3.785 accepted</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>The quantity box on an expense only took two decimals, so a jug size such as 3.785 L stopped the form from saving. Any decimal is accepted now, a quantity under 0.01 gets a plain message, and a problem on a line shows as 'Line 2: ...' instead of Save silently doing nothing.</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>Merge a duplicate engine into the one it copies</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>An engine used on past jobs, such as the inactive Cummins ISC/ISL/ISB duplicate, could not be deleted. Deleting it now offers Merge: its jobs move to the engine you keep and the duplicate is removed. The kept engine's prices don't change.</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Pricing &amp; Catalogue</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Bundled parts show $0 With Service again</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>Bundled filters now show $0.00 for With Service on the All filter sell price list (printed too) and in the part editor, with the calculated price in small text underneath, so both numbers are visible. On a job a bundled part still charges $0.</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>Add package opens faster</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>The package list on a job made two trips to the database one after the other; it now makes one. Reopening the package or part list within a minute shows the last results straight away, and a comma or full stop in the search no longer breaks it.</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Trans &amp; Diff search waits until you stop typing</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>Every letter typed in the Trans &amp; Diff search sent its own request, and they queued up behind each other. It now searches once you pause, like the other lists. Choosing a customer also no longer loads their store credit twice, which was holding up the lists.</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Oil groups priced from their most expensive oil</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>A group can now price itself from its most expensive active oil. Bulk uses the highest cost per litre; gallons use the highest cost per litre times each oil's own jug size, since jugs aren't all the same size. It updates by itself when an oil's cost changes or an oil joins or leaves the group. Switched on per group - Gear &amp; Trans stays manual.</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Charged rate ignores switched-off groups</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>The Oil types list showed a group's rate even when the group was switched off, although jobs don't use it. It now shows the rate a job line actually starts at.</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Store credit note matches the payment section</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>When editing an invoice, the store-credit note at the top and the payment section could show different amounts. Both now show the same figure: the credit available to this invoice.</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Upper &amp; Lower deck analytics</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>Analytics &gt; Job Duration now has an Upper &amp; Lower deck section: how many jobs have each deck filled in, jobs, sales and average time per technician on each deck, their most common services, who works together, and a weekly trend. A Technician filter narrows it to one person, and it's in the CSV.</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Job analytics CSV respects the Analytics permission</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>The Job Duration CSV could be downloaded from a direct link by anyone signed in. It now needs Analytics access, since it includes sales per technician.</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E235" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>EI, CPP and CPP2 typed in on each entry</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>The rates change too often for the automatic calculation, so each payroll entry now takes EI, CPP and CPP2 amounts - employee and employer side. The employer side fills in as you type, Estimate from rates gives a starting point, and the switches still mark who is exempt. Vacation pay and WSIB are still calculated.</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>Filter cost on Oil detail comes from the package</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>Filter cost now uses the filters in the engine's package at the package's quantities, so LF17503 x 2 counts twice (Volvo D12/D13 With Fleetguard: $86.91 instead of $68.79). An engine with no package filters still uses its own filter set, marked *, and the two are never added together.</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Part categories say what they count as</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Each part category now has a 'Counts as' setting - Filter, Oil, Fuel, Grease or Other - which decides which cost column its parts land in on the oil pages. It was filled in from the category names and can be changed in Part categories.</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F238" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>Double filters fixed on the engine filter sets</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Seven engines had a filter the Excel lists twice saved as one (the Volvo D12, Mack and Detroit 60 filter sets). Their quantities now match the linked package, which also corrects the Oil-change grid and Print list for those engines.</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Volume tier premium added to oil on a job</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>Oil added with Add oil now gets its volume tier premium as one extra line - e.g. $25 for 21 L and up - worked out from the litres of each oil on the job (gallon jugs converted to litres). It updates as the oil changes, and prints under Miscellaneous on the invoice.</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E240" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F240" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Grease-only job fee</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>A job that is only greasing - no oil, filters, fuel or Trans &amp; Diff - gets the grease-only fee set in Pricing defaults as its own line. It isn't charged on a free-grease visit, and staff can edit or remove it for a job.</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Gallon oil on a job deducts the right litres</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Selling 3 jugs of oil on a job took 3 L off stock instead of about 13.6 L. Gallon lines now deduct the jug size of that oil, and the job remembers whether a line was bulk or gallon.</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Opening an old oil-change job no longer re-prices it</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>Opening a saved oil-change job with no line items replaced its sub total with today's catalogue price as soon as the page loaded. It now only re-prices when the engine, oil or container is changed.</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E243" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F243" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>Trans &amp; Diff, promotion and part lists reopen instantly</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Reopening these lists on a job within a minute shows the last results straight away instead of waiting on the server again.</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>Line items no longer redraw on every keystroke</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Typing in any field of a job used to redraw the whole line-items table. It now only redraws when the lines change.</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E245" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>Optional faster network check</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Every page and action checked the approved-network list in the database. With a new IP_VERDICT_SECRET setting, an approved check is remembered for 5 minutes, so most requests skip it. Off until the setting is added.</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>Ready to release</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F222"/>
-  <conditionalFormatting sqref="A2:E191">
+  <autoFilter ref="A1:F246"/>
+  <conditionalFormatting sqref="A2:E246">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F2="Feature"</formula>
     </cfRule>
@@ -7301,7 +8021,7 @@
       <formula>$F2="Bug"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F191">
+  <conditionalFormatting sqref="F2:F246">
     <cfRule type="expression" priority="2" dxfId="3">
       <formula>$F2="Feature"</formula>
     </cfRule>
@@ -7342,7 +8062,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>221 tasks · 2026-05-30 to 2026-09-11</t>
+          <t>245 tasks · 2026-05-30 to 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -7360,7 +8080,7 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -7370,7 +8090,7 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -7380,7 +8100,7 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -7500,16 +8220,16 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -7530,7 +8250,7 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -7540,7 +8260,7 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -7560,27 +8280,27 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Vendors &amp; Expenses</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Vendors &amp; Expenses</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -7590,7 +8310,7 @@
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -7600,33 +8320,33 @@
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="B26" s="22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>UI &amp; Navigation</t>
+          <t>Pricing &amp; Catalogue</t>
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Pricing &amp; Catalogue</t>
+          <t>Packages</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
@@ -7636,21 +8356,21 @@
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>UI &amp; Navigation</t>
         </is>
       </c>
       <c r="B29" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -7660,7 +8380,7 @@
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/doc/QTL - Task Tracker (June 2026).xlsx
+++ b/doc/QTL - Task Tracker (June 2026).xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$246</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,9 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -615,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F246"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7336,7 +7335,7 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E224" s="6" t="n">
@@ -7366,7 +7365,7 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E225" s="6" t="n">
@@ -7396,7 +7395,7 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E226" s="6" t="n">
@@ -7426,7 +7425,7 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E227" s="6" t="n">
@@ -7456,7 +7455,7 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E228" s="6" t="n">
@@ -7486,7 +7485,7 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E229" s="6" t="n">
@@ -7516,7 +7515,7 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E230" s="6" t="n">
@@ -7546,7 +7545,7 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E231" s="6" t="n">
@@ -7576,7 +7575,7 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E232" s="6" t="n">
@@ -7606,7 +7605,7 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E233" s="6" t="n">
@@ -7636,7 +7635,7 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E234" s="6" t="n">
@@ -7666,7 +7665,7 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E235" s="6" t="n">
@@ -7696,7 +7695,7 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E236" s="6" t="n">
@@ -7726,7 +7725,7 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E237" s="6" t="n">
@@ -7756,7 +7755,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E238" s="6" t="n">
@@ -7786,7 +7785,7 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E239" s="6" t="n">
@@ -7816,7 +7815,7 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E240" s="6" t="n">
@@ -7846,7 +7845,7 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E241" s="6" t="n">
@@ -7876,7 +7875,7 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E242" s="6" t="n">
@@ -7906,7 +7905,7 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E243" s="6" t="n">
@@ -7936,7 +7935,7 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E244" s="6" t="n">
@@ -7966,7 +7965,7 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E245" s="6" t="n">
@@ -7996,7 +7995,7 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Ready to release</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="E246" s="6" t="n">
@@ -8008,9 +8007,309 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>Engines with two filter brands combined into one</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>An engine sold with a choice of filter brand was entered once per brand - 'Cat C12/3406 With Cat Filter' and '... With Fleetguard Filter' - and 13 engines were doubled up that way. Each is now one engine with filter options: every option is a package with its own name, oil capacity and prices, added and edited on the engine's page in Settings &gt; Engine types. The doubled-up engines were combined without changing any price - each option kept its own manual prices, locks, filters and past jobs.</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E247" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>Grid, Oil detail and Print list priced per filter option</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>The Oil-change grid, Oil detail and Print list show one row per engine, or one row per filter option for an engine sold with several, each with its own price. A Selling price set by hand is saved against that option.</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>Filter picked on the job for engines with options</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>On an oil-change job, an engine sold with a choice of filter now asks which filter. The price comes from that option, there is no price until it is picked, and the job remembers which one was sold.</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E249" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Tier premium counts as profit on Oil detail</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>The volume tier premium was counted as a cost, which made Profit look lower than it is. It is charged to the customer, so it now counts toward Profit alongside labour. Total cost is filter + oil + fuel + grease, and each Profit cell is compared with 'labour + tier'.</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>Min / max stock set per shop</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>Minimum and maximum stock were one number per part or oil, compared with the total across every shop, so Fort Erie down to 2 of a filter while Ayr held 20 read as fine. Each shop now has its own min and max beside its count, on both the Parts and Oils tabs, and is flagged low or over against its own numbers. The six parts that already had thresholds got them at every shop. Only Owner and Co-owner can change thresholds.</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E251" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>Cheque number and pay date on each entry</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>Each payroll entry now has a Cheque no. and a Pay date, filled in with the rest of the pay. They show under the employee's name on the pay week and print on the pay stub, the register and the CSV.</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F252" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Vendors &amp; Expenses</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Mark several expenses paid at once</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>Tick unpaid expenses on the Expenses list and mark them all paid with one payment date, mode and reference. Each is paid in full for what it still owes at that moment. Any that turn out to be already paid or outside your shops are skipped and counted, and the rest still go through.</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E253" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Supervisors and Technicians can save jobs again</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>Saving a job, an expense, a customer or a vehicle checked for Manager or Staff and turned away Supervisors and Technicians, although their pages and the database allowed it. A Supervisor now counts as a Manager and a Technician as Staff for every such check, and a Technician can sell past a stock shortfall the way Staff can.</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E254" s="6" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F254" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>Save on a user no longer does nothing</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>Save in Settings &gt; Users did nothing when a check failed on the other tab, or on a field with no box such as an older 'Multiple' shop list holding only one shop. It now says what is wrong and switches to the Profile tab.</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E255" s="6" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Reverse a payment on an invoice</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>Owners can reverse a recorded payment - a bounced cheque, or one posted to the wrong invoice such as TXN-006190 on invoice 329031 - from the invoice's payment history. The invoice goes back to Partial or Outstanding, any store credit the payment created is taken back, and the reversal stays in the audit log.</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E256" s="6" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F256" s="8" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F246"/>
-  <conditionalFormatting sqref="A2:E246">
+  <autoFilter ref="A1:F256"/>
+  <conditionalFormatting sqref="A2:E256">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F2="Feature"</formula>
     </cfRule>
@@ -8021,7 +8320,7 @@
       <formula>$F2="Bug"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F246">
+  <conditionalFormatting sqref="F2:F256">
     <cfRule type="expression" priority="2" dxfId="3">
       <formula>$F2="Feature"</formula>
     </cfRule>
@@ -8042,7 +8341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8062,7 +8361,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>245 tasks · 2026-05-30 to 2026-09-18</t>
+          <t>255 tasks · 2026-05-30 to 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8379,7 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -8090,7 +8389,7 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -8100,7 +8399,7 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -8220,143 +8519,148 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>By area</t>
         </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>Sales &amp; Jobs</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>Parts &amp; Pricing</t>
+          <t>Sales &amp; Jobs</t>
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>Customer &amp; Vehicle</t>
+          <t>Parts &amp; Pricing</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions</t>
+          <t>Customer &amp; Vehicle</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>Vendors &amp; Expenses</t>
+          <t>Roles &amp; Permissions</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Oil Grid &amp; Pricing</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>Oil Grid &amp; Pricing</t>
+          <t>Vendors &amp; Expenses</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="B26" s="22" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>Pricing &amp; Catalogue</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>Pricing &amp; Catalogue</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>UI &amp; Navigation</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="B29" s="22" t="n">
@@ -8366,20 +8670,30 @@
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Packages</t>
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
+          <t>UI &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
           <t>Dashboard &amp; Analytics</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B32" s="22" t="n">
         <v>4</v>
       </c>
     </row>
